--- a/output/pdf_financials_xlsx/ETI.xlsx
+++ b/output/pdf_financials_xlsx/ETI.xlsx
@@ -1926,13 +1926,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0.75</v>
+        <v>6.822314</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.75</v>
+        <v>6.822314</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.75</v>
+        <v>6.822314</v>
       </c>
     </row>
     <row r="93">
@@ -3318,7 +3318,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="n">
         <v>6.072314</v>
       </c>

--- a/output/pdf_financials_xlsx/ETI.xlsx
+++ b/output/pdf_financials_xlsx/ETI.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.001021</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001802</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000407</v>
       </c>
     </row>
     <row r="13">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.84239</v>
+        <v>-0.843411</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.945275</v>
+        <v>-0.9470769999999999</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.299918</v>
+        <v>-0.300325</v>
       </c>
     </row>
     <row r="28">
@@ -899,13 +899,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.84239</v>
+        <v>-0.843411</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.945275</v>
+        <v>-0.9470769999999999</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.299918</v>
+        <v>-0.300325</v>
       </c>
     </row>
     <row r="30">
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.201281</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.01478</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.02192</v>
       </c>
     </row>
     <row r="35">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.201281</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.01478</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.02192</v>
       </c>
     </row>
     <row r="37">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.286108</v>
+        <v>0.084827</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.047576</v>
+        <v>0.032796</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.027851</v>
+        <v>0.005931</v>
       </c>
     </row>
     <row r="49">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">

--- a/output/pdf_financials_xlsx/ETI.xlsx
+++ b/output/pdf_financials_xlsx/ETI.xlsx
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-0.84239</v>
+        <v>-0.541461</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-0.945275</v>
+        <v>-0.936975</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-0.299918</v>
+        <v>-0.342658</v>
       </c>
     </row>
     <row r="21">
@@ -765,13 +765,13 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-0.300929</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>-0.0083</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>0.04274</v>
       </c>
     </row>
     <row r="22">
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.247387</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.232035</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.101911</v>
       </c>
     </row>
     <row r="29">
@@ -899,13 +899,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.843411</v>
+        <v>-0.596024</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.9470769999999999</v>
+        <v>-0.715042</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.300325</v>
+        <v>-0.198414</v>
       </c>
     </row>
     <row r="30">
@@ -1081,10 +1081,10 @@
         <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.02989</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.004987</v>
       </c>
     </row>
     <row r="41">
@@ -1097,10 +1097,10 @@
         <v>0.264986</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.038547</v>
+        <v>0.068437</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.008824</v>
+        <v>0.013811</v>
       </c>
     </row>
     <row r="42">
@@ -1209,10 +1209,10 @@
         <v>0.084827</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.032796</v>
+        <v>0.002906</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.005931</v>
+        <v>0.000944</v>
       </c>
     </row>
     <row r="49">
@@ -1468,13 +1468,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.165255</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.185305</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.34916</v>
       </c>
     </row>
     <row r="65">
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.08638700000000001</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="68">
@@ -2028,20 +2028,14 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.84239</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-0.945275</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-0.299918</v>
       </c>
     </row>
     <row r="100">
@@ -2050,20 +2044,14 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2072,20 +2060,14 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>-0.141823</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0.222339</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0.008822999999999999</v>
       </c>
     </row>
     <row r="102">
@@ -2094,20 +2076,14 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0.0268</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2116,20 +2092,14 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0.024377</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0.036931</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>0.013165</v>
       </c>
     </row>
     <row r="104">
@@ -2138,20 +2108,14 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>-0.234709</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>-0.062135</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>0.162799</v>
       </c>
     </row>
     <row r="105">
@@ -2160,20 +2124,14 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2182,20 +2140,14 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>-0.325355</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>0.197135</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>0.184787</v>
       </c>
     </row>
     <row r="107">
@@ -2204,20 +2156,14 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0.003689</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -2226,20 +2172,14 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2248,20 +2188,14 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2270,20 +2204,14 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2292,20 +2220,14 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2314,20 +2236,14 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0.045699</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0.148527</v>
       </c>
     </row>
     <row r="113">
@@ -2336,20 +2252,14 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2358,20 +2268,14 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2380,20 +2284,14 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0.09984800000000001</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0.0209</v>
       </c>
     </row>
     <row r="116">
@@ -2402,20 +2300,14 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2424,20 +2316,14 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2446,20 +2332,14 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2468,20 +2348,14 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>1.239805</v>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>0.09984800000000001</v>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>0.169427</v>
       </c>
     </row>
     <row r="120">
@@ -2490,20 +2364,14 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2512,20 +2380,14 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2534,20 +2396,14 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2556,20 +2412,14 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2578,20 +2428,14 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -2600,20 +2444,14 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -2622,20 +2460,14 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -2666,20 +2498,14 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -2688,20 +2514,14 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>-0.140473</v>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>-0.074821</v>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>-0.033675</v>
       </c>
     </row>
     <row r="130">
@@ -2710,20 +2530,14 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0.429038</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>0.201281</v>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>0.01478</v>
       </c>
     </row>
     <row r="131">
@@ -2732,20 +2546,14 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -2754,20 +2562,14 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-0.227757</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>-0.186501</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>0.00714</v>
       </c>
     </row>
     <row r="133">
@@ -2776,20 +2578,14 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.201281</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>0.01478</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>0.02192</v>
       </c>
     </row>
     <row r="134">
@@ -2798,20 +2594,14 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -2820,20 +2610,14 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-1.427094</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>-0.226628</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>-0.142312</v>
       </c>
     </row>
   </sheetData>
@@ -2847,7 +2631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3710,137 +3494,143 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Operating costs</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
-        <v>0.101938</v>
+        <v>-0.84239</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.040376</v>
+        <v>-0.945275</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.013978</v>
+        <v>-0.299918</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Management and employee costs 13, 15</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0.247387</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.420709</v>
+        <v>0.232035</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.076742</v>
+        <v>0.101911</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>General and administration 15</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Foreign exchange (gain) loss</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.384762</v>
+        <v>0.045798</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.15755</v>
+        <v>-0.031068</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Operating expenses total</t>
+          <t>Gain on forgiveness of accounts payable</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>1.395291</v>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.845847</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>0.24827</v>
+        <v>-0.005381</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bank service charge</t>
+          <t>Gain on disposal of investments</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -3850,248 +3640,246 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>-0.004103</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>-0.003651</v>
+        <v>-0.120748</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Depreciation 8</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>-0.247387</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>-0.232035</v>
+          <t>Loss on disposal of plant, property and equipment</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.101911</v>
+        <v>0.028599</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss)</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" s="5" t="n">
+        <v>0.026996</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>-0.045844</v>
+        <v>0.015143</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.031068</v>
+        <v>0.007492</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Gain on forgiveness of accounts payable</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Trade and other receivables</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>-0.141823</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.005381</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.222339</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.008822999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Gain on disposal of investments 7</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>Prepaid expenses and deposits</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.120748</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.036931</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.013165</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Loss on disposal of plant, property and equipment 8</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>-0.248465</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>-0.056754</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.028599</v>
+        <v>0.162799</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="n">
-        <v>0.001021</v>
+          <t>Due to related parties</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.001802</v>
+        <v>0.349284</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.000407</v>
+        <v>-0.134115</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Interest and financing costs 10,11</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>-1.427094</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>-0.015142</v>
+        <v>-0.226628</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.007492</v>
+        <v>-0.142312</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Proceeds from sale of investment 7</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>SaleOfInvestment</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4100,362 +3888,366 @@
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.00066</v>
+        <v>0.09984800000000001</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.005211</v>
+        <v>0.0209</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Other recoveries</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="n">
-        <v>0.077405</v>
+          <t>Proceeds from disposals of property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0.045699</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.010579</v>
+        <v>0.148527</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Other income (expenses) total</t>
+          <t>Cash provided by investing activities</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.85383</v>
+        <v>1.239805</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.091128</v>
+        <v>0.09984800000000001</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.094388</v>
+        <v>0.169427</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Loss from continuing operations</t>
+          <t>Proceeds from subscription receivable</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" s="5" t="n">
-        <v>-0.541461</v>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>-0.936975</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>-0.342658</v>
+        <v>0.025</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Gain (loss) from discontinued operations 16</t>
+          <t>Payment of lease liabilities</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E44" s="5" t="n">
+        <v>-0.110473</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.09982099999999999</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.04274</v>
+        <v>-0.033675</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
+          <t>Cash used in financing activities</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>-0.84239</v>
+        <v>-0.140473</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>-0.945275</v>
+        <v>-0.074821</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.299918</v>
+        <v>-0.033675</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Net loss per share</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Net cash used in continuing operations</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-1.521868</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-0.201601</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0</v>
+        <v>-0.00656</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
+          <t>Net cash provided by discontinued operations 16</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" s="5" t="n">
-        <v>108.192228</v>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>113.60728</v>
+        <v>0.0151</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>113.60728</v>
+        <v>0.0137</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Management and employee costs 15,16</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E48" s="5" t="n">
-        <v>0.552094</v>
+        <v>0.429038</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0.420709</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.201281</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.01478</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>General and administration 15,17</t>
+          <t>Cash, end of year</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0.7375699999999999</v>
+        <v>0.201281</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.384762</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.01478</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.02192</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Share-based payments 14(c)</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>Cash interest paid</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E50" s="5" t="n">
-        <v>0.003689</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.007029</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>0.004103</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.003651</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Foreign exchange (loss) gain</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Cash interest received</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" s="5" t="n">
-        <v>0.003741</v>
+        <v>0.001021</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>-0.045844</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.00176</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>-0.000407</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Gain on disposal of plant, property and equipment 8</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" s="5" t="n">
-        <v>0.027846</v>
+          <t>Income taxes paid</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>IncomeTaxPaidSupplementalData</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4471,149 +4263,1672 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Gain on lease buyout 8,11</t>
+          <t>Balance, December 31, 2023 113,607,280 35,594,867 5,785,662 286,652 750,000</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" s="5" t="n">
-        <v>0.002496</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.057371</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>-0.057371</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>-42.474552</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Government subsidy 10</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>Net loss for the year - - - - -</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E54" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.84239</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>-0.945275</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>-0.945275</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Interest and financing costs 11,12,13</t>
+          <t>Balance, December 31, 2024 113,607,280 35,594,867 5,785,662 286,652 750,000</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" s="5" t="n">
-        <v>-0.033572</v>
+        <v>-1.002646</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>-0.019245</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.002646</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>-43.419827</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Reversal of contingent liability 19</t>
+          <t>Balance, December 31, 2025 113,607,280 35,594,867 5,785,662 286,652 750,000</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" s="5" t="n">
-        <v>1.089685</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>-1.302564</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>-43.719745</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0.003689</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0.045798</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Gain on disposal of investments 7</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>-0.120748</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Gain on disposal of PPE</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" s="5" t="n">
+        <v>-0.027846</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Gain on disposal of leases</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" s="5" t="n">
+        <v>-0.002496</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Government Subsidy</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" s="5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Reversal of provision</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" s="5" t="n">
+        <v>-1.089685</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Changes in non-cash working capital items</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Inventories</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ChangeInInventory</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>0.0268</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Changes in non-cash working capital items</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>0.024377</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>0.036931</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Changes in non-cash working capital items</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Due to related party</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" s="5" t="n">
+        <v>0.606362</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0.349284</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Proceeds from sale of investments 7</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>0.09984800000000001</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Repayment of loan payable</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" s="5" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Net cash provided by discontinued operations 18</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" s="5" t="n">
+        <v>1.294111</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>0.0151</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Supplemental cash flow information</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Reversal of accrued unit issuance costs from accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>0.005874</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Supplemental cash flow information</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Purchase of property, plant and equipment in accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>0.007882</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2022 107,928,458 35,333,446 5,781,973 258,258 750,000</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" s="5" t="n">
+        <v>0.491515</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>-41.632162</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Units issued in private placement 2,100,000 94,500 - 10,500 -</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" s="5" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Units issued to settle convertible notes 3,578,822 161,047 - 17,894 -</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" s="5" t="n">
+        <v>0.178941</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Reversal of unit issuance costs - 5,874 - - -</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" s="5" t="n">
+        <v>0.005874</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Share-based payments - - 3,689 - -</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" s="5" t="n">
+        <v>0.003689</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Operating costs</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" s="5" t="n">
+        <v>0.101938</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>0.040376</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0.013978</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Management and employee costs 13, 15</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>0.420709</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>0.076742</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>General and administration 15</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>0.384762</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>0.15755</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Operating expenses total</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>1.395291</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>0.845847</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>0.24827</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
         <is>
           <t>Other income (expenses)</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Bank service charge</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>-0.004103</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>-0.003651</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Depreciation 8</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>-0.247387</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>-0.232035</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>-0.101911</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Foreign exchange gain (loss)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>-0.045844</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.031068</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Gain on forgiveness of accounts payable</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>0.005381</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Gain on disposal of investments 7</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>0.120748</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Loss on disposal of plant, property and equipment 8</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>-0.028599</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>0.001021</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>0.001802</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0.000407</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Interest and financing costs 10,11</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>-0.015142</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>-0.007492</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>0.00066</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0.005211</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Other recoveries</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>0.077405</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0.010579</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Other income (expenses) total</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>0.85383</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>0.091128</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0.094388</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Loss from continuing operations</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>-0.541461</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>-0.936975</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>-0.342658</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Gain (loss) from discontinued operations 16</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>-0.0083</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>0.04274</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>-0.84239</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>-0.945275</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>-0.299918</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Net loss per share</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" s="5" t="n">
+        <v>108.192228</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>113.60728</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>113.60728</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Management and employee costs 15,16</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" s="5" t="n">
+        <v>0.552094</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>0.420709</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>General and administration 15,17</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="n">
+        <v>0.7375699999999999</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>0.384762</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Share-based payments 14(c)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" s="5" t="n">
+        <v>0.003689</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Foreign exchange (loss) gain</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="n">
+        <v>0.003741</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>-0.045844</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Gain on disposal of plant, property and equipment 8</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" s="5" t="n">
+        <v>0.027846</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Gain on lease buyout 8,11</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" s="5" t="n">
+        <v>0.002496</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Government subsidy 10</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Interest and financing costs 11,12,13</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" s="5" t="n">
+        <v>-0.033572</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>-0.019245</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Reversal of contingent liability 19</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" s="5" t="n">
+        <v>1.089685</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
         <is>
           <t>Loss from discontinued operations 18</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" s="5" t="n">
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="n">
         <v>-0.300929</v>
       </c>
-      <c r="F57" s="5" t="n">
+      <c r="F106" s="5" t="n">
         <v>-0.0083</v>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t>-</t>
         </is>
